--- a/data/trans_orig/ProbViv_temp-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Habitat-trans_orig.xlsx
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47016</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>88738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>68983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>85786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93396</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114806</t>
+          <t>114112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167665</t>
+          <t>168955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195840</t>
+          <t>195858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>72776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98391</t>
+          <t>98329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88771</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117239</t>
+          <t>119144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169969</t>
+          <t>169622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210015</t>
+          <t>209633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91122</t>
+          <t>91184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115756</t>
+          <t>116737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>135891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166264</t>
+          <t>164919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234533</t>
+          <t>234915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274579</t>
+          <t>274926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>63416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123910</t>
+          <t>126447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67730</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114637</t>
+          <t>116341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206400</t>
+          <t>203265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66491</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126747</t>
+          <t>126985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117556</t>
+          <t>116934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142307</t>
+          <t>143277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169287</t>
+          <t>172422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261050</t>
+          <t>259346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67364</t>
+          <t>65700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89603</t>
+          <t>88960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79165</t>
+          <t>78863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103610</t>
+          <t>102787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152157</t>
+          <t>152168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185314</t>
+          <t>184597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100598</t>
+          <t>102262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>77508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101130</t>
+          <t>101432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162943</t>
+          <t>163660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196100</t>
+          <t>196089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257984</t>
+          <t>256029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342875</t>
+          <t>338376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>312103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>532894</t>
+          <t>535925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>629449</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322281</t>
+          <t>326780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407172</t>
+          <t>409127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>448925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>500405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>796735</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>893290</t>
+          <t>890259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_temp-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3126,47 +3126,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3469,47 +3469,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3812,47 +3812,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4155,47 +4155,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5073,47 +5073,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5416,47 +5416,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5759,47 +5759,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6102,47 +6102,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36239</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27294</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46974</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38625</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31494</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48297</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36683</t>
+          <t>40669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75308</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>61933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88738</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89667</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78932</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98612</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>78655</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68983</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85786</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>67,07%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>80402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92554</t>
+          <t>71167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114112</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>182385</t>
+          <t>170069</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168955</t>
+          <t>157416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195858</t>
+          <t>185044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>98915</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85028</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113531</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>84931</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>72776</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>98329</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>79953</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119144</t>
+          <t>93136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>188618</t>
+          <t>178868</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>160918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209633</t>
+          <t>197508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>123675</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152178</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>104582</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91184</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>116737</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>55,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>151347</t>
+          <t>103384</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135891</t>
+          <t>90201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164919</t>
+          <t>114264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>255930</t>
+          <t>241675</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234915</t>
+          <t>223035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274926</t>
+          <t>259625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47872</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36808</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60313</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85499</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>63416</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>126447</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54589</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42009</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>64824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140202</t>
+          <t>102461</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116341</t>
+          <t>87079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203265</t>
+          <t>119857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120469</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108028</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131533</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>104902</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63954</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126985</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>130583</t>
+          <t>102461</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>92226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>112789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>235485</t>
+          <t>222930</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172422</t>
+          <t>205534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259346</t>
+          <t>238312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86976</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75121</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97501</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>51,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77509</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65700</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>88960</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>46,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91715</t>
+          <t>80077</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78863</t>
+          <t>69196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102787</t>
+          <t>91151</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>169224</t>
+          <t>167053</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152168</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184597</t>
+          <t>182058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70918</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>93298</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>48,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>90453</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79002</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102262</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77508</t>
+          <t>75994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>97949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>179033</t>
+          <t>168511</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163660</t>
+          <t>153506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196089</t>
+          <t>185458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>270003</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>243222</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>292631</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>286563</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>256029</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>338376</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260623</t>
+          <t>234289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>312103</t>
+          <t>274834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>535925</t>
+          <t>493395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>633137</t>
+          <t>557944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>429869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>407241</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>456650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>574</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>378593</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>326780</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>409127</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>474239</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448925</t>
+          <t>353769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500405</t>
+          <t>394314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>852832</t>
+          <t>803185</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>793047</t>
+          <t>770531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890259</t>
+          <t>835080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
